--- a/trace_compare_final_prefix_code_project_SS/corrected_added_highlight_prefix_logic_output.xlsx
+++ b/trace_compare_final_prefix_code_project_SS/corrected_added_highlight_prefix_logic_output.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\MM_Repo\trace_compare_final_prefix_code_project_SS\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\New folder\MM_Automation\MottM_Automation\trace_compare_final_prefix_code_project_SS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7E96EEB3-02D8-478D-8813-11E2D944C20D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AF260C44-9D58-4ECD-8981-F99A2CA8CD50}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="24196" windowHeight="14476" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="51420" windowHeight="21100" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1_new" sheetId="2" r:id="rId1"/>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="476" uniqueCount="97">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="492" uniqueCount="100">
   <si>
     <t>Part B: Technical Requirements</t>
   </si>
@@ -312,6 +312,15 @@
   </si>
   <si>
     <t>PETERPORKER</t>
+  </si>
+  <si>
+    <t>Project-PS&amp;TR-B-000126</t>
+  </si>
+  <si>
+    <t>Punshi</t>
+  </si>
+  <si>
+    <t>Raval</t>
   </si>
 </sst>
 </file>
@@ -515,12 +524,12 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -832,13 +841,13 @@
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:O34"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <dimension ref="A1:O35"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="15" width="30.59765625" style="6" bestFit="1" customWidth="1"/>
+    <col min="1" max="15" width="30.6328125" style="6" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" s="1" customFormat="1" ht="33" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:15" s="1" customFormat="1" ht="33" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -885,20 +894,20 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:15" s="1" customFormat="1" ht="57.75" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A2" s="14" t="s">
+    <row r="2" spans="1:15" s="1" customFormat="1" ht="57.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A2" s="11" t="s">
         <v>9</v>
       </c>
-      <c r="B2" s="11"/>
-      <c r="C2" s="11"/>
-      <c r="D2" s="14" t="s">
+      <c r="B2" s="14"/>
+      <c r="C2" s="14"/>
+      <c r="D2" s="11" t="s">
         <v>10</v>
       </c>
-      <c r="E2" s="11"/>
-      <c r="F2" s="11"/>
-      <c r="G2" s="14"/>
-      <c r="H2" s="11"/>
-      <c r="I2" s="11"/>
+      <c r="E2" s="14"/>
+      <c r="F2" s="14"/>
+      <c r="G2" s="11"/>
+      <c r="H2" s="14"/>
+      <c r="I2" s="14"/>
       <c r="J2" s="4" t="s">
         <v>11</v>
       </c>
@@ -918,7 +927,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="3" spans="1:15" s="1" customFormat="1" ht="70.5" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:15" s="1" customFormat="1" ht="70.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="13"/>
       <c r="B3" s="13"/>
       <c r="C3" s="13"/>
@@ -947,28 +956,28 @@
         <v>16</v>
       </c>
     </row>
-    <row r="4" spans="1:15" s="1" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A4" s="14" t="s">
+    <row r="4" spans="1:15" s="1" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A4" s="11" t="s">
         <v>21</v>
       </c>
-      <c r="B4" s="11"/>
-      <c r="C4" s="11"/>
-      <c r="D4" s="14" t="s">
+      <c r="B4" s="14"/>
+      <c r="C4" s="14"/>
+      <c r="D4" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="E4" s="11" t="s">
+      <c r="E4" s="14" t="s">
         <v>23</v>
       </c>
-      <c r="F4" s="11" t="s">
+      <c r="F4" s="14" t="s">
         <v>24</v>
       </c>
-      <c r="G4" s="14" t="s">
+      <c r="G4" s="11" t="s">
         <v>25</v>
       </c>
-      <c r="H4" s="11" t="s">
+      <c r="H4" s="14" t="s">
         <v>26</v>
       </c>
-      <c r="I4" s="11" t="s">
+      <c r="I4" s="14" t="s">
         <v>27</v>
       </c>
       <c r="J4" s="4" t="s">
@@ -990,7 +999,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="5" spans="1:15" s="1" customFormat="1" ht="57.75" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:15" s="1" customFormat="1" ht="57.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="12"/>
       <c r="B5" s="12"/>
       <c r="C5" s="12"/>
@@ -1019,7 +1028,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="6" spans="1:15" s="1" customFormat="1" ht="70.5" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:15" s="1" customFormat="1" ht="70.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="12"/>
       <c r="B6" s="12"/>
       <c r="C6" s="12"/>
@@ -1048,20 +1057,20 @@
         <v>16</v>
       </c>
     </row>
-    <row r="7" spans="1:15" s="1" customFormat="1" ht="57.75" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:15" s="1" customFormat="1" ht="57.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A7" s="12"/>
       <c r="B7" s="12"/>
       <c r="C7" s="12"/>
       <c r="D7" s="12"/>
       <c r="E7" s="12"/>
       <c r="F7" s="12"/>
-      <c r="G7" s="14" t="s">
+      <c r="G7" s="11" t="s">
         <v>37</v>
       </c>
-      <c r="H7" s="11" t="s">
+      <c r="H7" s="14" t="s">
         <v>38</v>
       </c>
-      <c r="I7" s="11" t="s">
+      <c r="I7" s="14" t="s">
         <v>39</v>
       </c>
       <c r="J7" s="4" t="s">
@@ -1083,7 +1092,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="8" spans="1:15" s="1" customFormat="1" ht="57.75" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:15" s="1" customFormat="1" ht="57.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8" s="12"/>
       <c r="B8" s="12"/>
       <c r="C8" s="12"/>
@@ -1112,7 +1121,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="9" spans="1:15" s="1" customFormat="1" ht="57.75" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:15" s="1" customFormat="1" ht="57.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A9" s="12"/>
       <c r="B9" s="12"/>
       <c r="C9" s="12"/>
@@ -1141,7 +1150,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="10" spans="1:15" s="1" customFormat="1" ht="70.5" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:15" s="1" customFormat="1" ht="70.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A10" s="12"/>
       <c r="B10" s="12"/>
       <c r="C10" s="12"/>
@@ -1170,7 +1179,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="11" spans="1:15" s="1" customFormat="1" ht="57.75" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:15" s="1" customFormat="1" ht="57.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A11" s="12"/>
       <c r="B11" s="12"/>
       <c r="C11" s="12"/>
@@ -1199,20 +1208,20 @@
         <v>16</v>
       </c>
     </row>
-    <row r="12" spans="1:15" s="1" customFormat="1" ht="57.75" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="12" spans="1:15" s="1" customFormat="1" ht="57.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A12" s="12"/>
       <c r="B12" s="12"/>
       <c r="C12" s="12"/>
       <c r="D12" s="12"/>
       <c r="E12" s="12"/>
       <c r="F12" s="12"/>
-      <c r="G12" s="14" t="s">
+      <c r="G12" s="11" t="s">
         <v>49</v>
       </c>
-      <c r="H12" s="11" t="s">
+      <c r="H12" s="14" t="s">
         <v>50</v>
       </c>
-      <c r="I12" s="11" t="s">
+      <c r="I12" s="14" t="s">
         <v>51</v>
       </c>
       <c r="J12" s="4" t="s">
@@ -1234,7 +1243,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="13" spans="1:15" s="1" customFormat="1" ht="57.75" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="13" spans="1:15" s="1" customFormat="1" ht="57.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A13" s="12"/>
       <c r="B13" s="12"/>
       <c r="C13" s="12"/>
@@ -1263,7 +1272,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="14" spans="1:15" s="1" customFormat="1" ht="57.75" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="14" spans="1:15" s="1" customFormat="1" ht="57.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A14" s="12"/>
       <c r="B14" s="12"/>
       <c r="C14" s="12"/>
@@ -1292,7 +1301,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="15" spans="1:15" s="1" customFormat="1" ht="57.75" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="15" spans="1:15" s="1" customFormat="1" ht="57.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A15" s="12"/>
       <c r="B15" s="12"/>
       <c r="C15" s="12"/>
@@ -1321,20 +1330,20 @@
         <v>16</v>
       </c>
     </row>
-    <row r="16" spans="1:15" s="1" customFormat="1" ht="70.5" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="16" spans="1:15" s="1" customFormat="1" ht="70.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A16" s="12"/>
       <c r="B16" s="12"/>
       <c r="C16" s="12"/>
-      <c r="D16" s="14"/>
-      <c r="E16" s="11"/>
-      <c r="F16" s="11"/>
-      <c r="G16" s="14" t="s">
+      <c r="D16" s="11"/>
+      <c r="E16" s="14"/>
+      <c r="F16" s="14"/>
+      <c r="G16" s="11" t="s">
         <v>61</v>
       </c>
-      <c r="H16" s="11" t="s">
+      <c r="H16" s="14" t="s">
         <v>62</v>
       </c>
-      <c r="I16" s="11" t="s">
+      <c r="I16" s="14" t="s">
         <v>63</v>
       </c>
       <c r="J16" s="4" t="s">
@@ -1356,7 +1365,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="17" spans="1:15" s="1" customFormat="1" ht="57.75" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="17" spans="1:15" s="1" customFormat="1" ht="57.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A17" s="12"/>
       <c r="B17" s="12"/>
       <c r="C17" s="12"/>
@@ -1385,7 +1394,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="18" spans="1:15" s="1" customFormat="1" ht="57.75" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="18" spans="1:15" s="1" customFormat="1" ht="57.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A18" s="12"/>
       <c r="B18" s="12"/>
       <c r="C18" s="12"/>
@@ -1414,7 +1423,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="19" spans="1:15" s="1" customFormat="1" ht="70.5" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="19" spans="1:15" s="1" customFormat="1" ht="70.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A19" s="12"/>
       <c r="B19" s="12"/>
       <c r="C19" s="12"/>
@@ -1443,7 +1452,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="20" spans="1:15" s="1" customFormat="1" ht="57.75" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="20" spans="1:15" s="1" customFormat="1" ht="57.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A20" s="12"/>
       <c r="B20" s="12"/>
       <c r="C20" s="12"/>
@@ -1472,7 +1481,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="21" spans="1:15" s="1" customFormat="1" ht="70.5" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="21" spans="1:15" s="1" customFormat="1" ht="70.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A21" s="12"/>
       <c r="B21" s="12"/>
       <c r="C21" s="12"/>
@@ -1501,7 +1510,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="22" spans="1:15" s="1" customFormat="1" ht="57.75" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="22" spans="1:15" s="1" customFormat="1" ht="57.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A22" s="12"/>
       <c r="B22" s="12"/>
       <c r="C22" s="12"/>
@@ -1530,16 +1539,16 @@
         <v>16</v>
       </c>
     </row>
-    <row r="23" spans="1:15" s="1" customFormat="1" ht="57.75" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="23" spans="1:15" s="1" customFormat="1" ht="57.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A23" s="12"/>
       <c r="B23" s="12"/>
       <c r="C23" s="12"/>
       <c r="D23" s="12"/>
       <c r="E23" s="12"/>
       <c r="F23" s="12"/>
-      <c r="G23" s="14"/>
-      <c r="H23" s="11"/>
-      <c r="I23" s="11"/>
+      <c r="G23" s="11"/>
+      <c r="H23" s="14"/>
+      <c r="I23" s="14"/>
       <c r="J23" s="4" t="s">
         <v>70</v>
       </c>
@@ -1559,7 +1568,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="24" spans="1:15" s="1" customFormat="1" ht="57.75" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="24" spans="1:15" s="1" customFormat="1" ht="57.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A24" s="13"/>
       <c r="B24" s="13"/>
       <c r="C24" s="13"/>
@@ -1588,7 +1597,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="25" spans="1:15" s="1" customFormat="1" ht="57.75" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="25" spans="1:15" s="1" customFormat="1" ht="57.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A25" s="4" t="s">
         <v>73</v>
       </c>
@@ -1619,7 +1628,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="26" spans="1:15" s="1" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="26" spans="1:15" s="1" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A26" s="4" t="s">
         <v>77</v>
       </c>
@@ -1638,7 +1647,7 @@
       <c r="N26" s="5"/>
       <c r="O26" s="5"/>
     </row>
-    <row r="27" spans="1:15" s="1" customFormat="1" ht="57.75" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="27" spans="1:15" s="1" customFormat="1" ht="57.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A27" s="4" t="s">
         <v>78</v>
       </c>
@@ -1669,7 +1678,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="28" spans="1:15" s="1" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="28" spans="1:15" s="1" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A28" s="4" t="s">
         <v>79</v>
       </c>
@@ -1688,7 +1697,7 @@
       <c r="N28" s="5"/>
       <c r="O28" s="5"/>
     </row>
-    <row r="29" spans="1:15" x14ac:dyDescent="0.45">
+    <row r="29" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A29" s="4" t="s">
         <v>80</v>
       </c>
@@ -1709,7 +1718,7 @@
       <c r="N29" s="5"/>
       <c r="O29" s="5"/>
     </row>
-    <row r="30" spans="1:15" x14ac:dyDescent="0.45">
+    <row r="30" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A30" s="7" t="s">
         <v>81</v>
       </c>
@@ -1728,7 +1737,7 @@
       <c r="N30" s="8"/>
       <c r="O30" s="8"/>
     </row>
-    <row r="31" spans="1:15" x14ac:dyDescent="0.45">
+    <row r="31" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A31" s="7" t="s">
         <v>85</v>
       </c>
@@ -1751,7 +1760,7 @@
       <c r="N31" s="8"/>
       <c r="O31" s="8"/>
     </row>
-    <row r="32" spans="1:15" x14ac:dyDescent="0.45">
+    <row r="32" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A32" s="7" t="s">
         <v>87</v>
       </c>
@@ -1768,15 +1777,14 @@
       <c r="J32" s="4" t="s">
         <v>83</v>
       </c>
-      <c r="K32" s="8" t="s">
+      <c r="L32" s="8" t="s">
         <v>90</v>
       </c>
-      <c r="L32" s="8"/>
       <c r="M32" s="8"/>
       <c r="N32" s="8"/>
       <c r="O32" s="8"/>
     </row>
-    <row r="33" spans="1:15" x14ac:dyDescent="0.45">
+    <row r="33" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A33" s="7" t="s">
         <v>91</v>
       </c>
@@ -1797,7 +1805,7 @@
       <c r="N33" s="8"/>
       <c r="O33" s="8"/>
     </row>
-    <row r="34" spans="1:15" x14ac:dyDescent="0.45">
+    <row r="34" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A34" s="7" t="s">
         <v>94</v>
       </c>
@@ -1818,8 +1826,58 @@
       <c r="N34" s="8"/>
       <c r="O34" s="8"/>
     </row>
+    <row r="35" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A35" s="7" t="s">
+        <v>97</v>
+      </c>
+      <c r="B35" s="8"/>
+      <c r="C35" s="8" t="s">
+        <v>92</v>
+      </c>
+      <c r="D35" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="E35" s="8"/>
+      <c r="F35" s="8" t="s">
+        <v>98</v>
+      </c>
+      <c r="G35" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="H35" s="8"/>
+      <c r="I35" s="8" t="s">
+        <v>90</v>
+      </c>
+      <c r="J35" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="K35" s="8"/>
+      <c r="L35" s="8" t="s">
+        <v>99</v>
+      </c>
+      <c r="M35" s="8"/>
+      <c r="N35" s="8"/>
+      <c r="O35" s="8"/>
+    </row>
   </sheetData>
   <mergeCells count="33">
+    <mergeCell ref="I4:I6"/>
+    <mergeCell ref="I23:I24"/>
+    <mergeCell ref="I7:I11"/>
+    <mergeCell ref="I12:I14"/>
+    <mergeCell ref="I16:I22"/>
+    <mergeCell ref="B2:B3"/>
+    <mergeCell ref="D2:D3"/>
+    <mergeCell ref="F2:F3"/>
+    <mergeCell ref="H2:H3"/>
+    <mergeCell ref="G4:G6"/>
+    <mergeCell ref="C4:C24"/>
+    <mergeCell ref="H4:H6"/>
+    <mergeCell ref="H23:H24"/>
+    <mergeCell ref="H7:H11"/>
+    <mergeCell ref="D16:D24"/>
+    <mergeCell ref="H12:H14"/>
+    <mergeCell ref="H16:H22"/>
     <mergeCell ref="I2:I3"/>
     <mergeCell ref="G23:G24"/>
     <mergeCell ref="B4:B24"/>
@@ -1836,23 +1894,6 @@
     <mergeCell ref="F16:F24"/>
     <mergeCell ref="G2:G3"/>
     <mergeCell ref="A4:A24"/>
-    <mergeCell ref="B2:B3"/>
-    <mergeCell ref="D2:D3"/>
-    <mergeCell ref="F2:F3"/>
-    <mergeCell ref="H2:H3"/>
-    <mergeCell ref="G4:G6"/>
-    <mergeCell ref="C4:C24"/>
-    <mergeCell ref="H4:H6"/>
-    <mergeCell ref="H23:H24"/>
-    <mergeCell ref="H7:H11"/>
-    <mergeCell ref="D16:D24"/>
-    <mergeCell ref="H12:H14"/>
-    <mergeCell ref="H16:H22"/>
-    <mergeCell ref="I4:I6"/>
-    <mergeCell ref="I23:I24"/>
-    <mergeCell ref="I7:I11"/>
-    <mergeCell ref="I12:I14"/>
-    <mergeCell ref="I16:I22"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <headerFooter>
@@ -1866,13 +1907,13 @@
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:O53"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <dimension ref="A1:O54"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="15" width="30.59765625" style="6" bestFit="1" customWidth="1"/>
+    <col min="1" max="15" width="30.6328125" style="6" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" s="1" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:15" s="1" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -1919,7 +1960,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:15" s="1" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:15" s="1" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="2" t="s">
         <v>84</v>
       </c>
@@ -1938,22 +1979,22 @@
       <c r="N2" s="3"/>
       <c r="O2" s="3"/>
     </row>
-    <row r="3" spans="1:15" s="1" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A3" s="14" t="s">
+    <row r="3" spans="1:15" s="1" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A3" s="11" t="s">
         <v>21</v>
       </c>
-      <c r="B3" s="11"/>
-      <c r="C3" s="11"/>
-      <c r="D3" s="14" t="s">
+      <c r="B3" s="14"/>
+      <c r="C3" s="14"/>
+      <c r="D3" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="E3" s="11" t="s">
+      <c r="E3" s="14" t="s">
         <v>23</v>
       </c>
-      <c r="F3" s="11" t="s">
+      <c r="F3" s="14" t="s">
         <v>24</v>
       </c>
-      <c r="G3" s="14"/>
+      <c r="G3" s="11"/>
       <c r="H3" s="15"/>
       <c r="I3" s="15"/>
       <c r="J3" s="4"/>
@@ -1963,7 +2004,7 @@
       <c r="N3" s="5"/>
       <c r="O3" s="5"/>
     </row>
-    <row r="4" spans="1:15" s="1" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:15" s="1" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="12"/>
       <c r="B4" s="12"/>
       <c r="C4" s="12"/>
@@ -1980,7 +2021,7 @@
       <c r="N4" s="5"/>
       <c r="O4" s="5"/>
     </row>
-    <row r="5" spans="1:15" s="1" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:15" s="1" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="12"/>
       <c r="B5" s="12"/>
       <c r="C5" s="12"/>
@@ -1997,20 +2038,20 @@
       <c r="N5" s="5"/>
       <c r="O5" s="5"/>
     </row>
-    <row r="6" spans="1:15" s="1" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:15" s="1" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="12"/>
       <c r="B6" s="12"/>
       <c r="C6" s="12"/>
       <c r="D6" s="12"/>
       <c r="E6" s="12"/>
       <c r="F6" s="12"/>
-      <c r="G6" s="14" t="s">
+      <c r="G6" s="11" t="s">
         <v>37</v>
       </c>
-      <c r="H6" s="11" t="s">
+      <c r="H6" s="14" t="s">
         <v>38</v>
       </c>
-      <c r="I6" s="11" t="s">
+      <c r="I6" s="14" t="s">
         <v>39</v>
       </c>
       <c r="J6" s="4" t="s">
@@ -2032,7 +2073,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="7" spans="1:15" s="1" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:15" s="1" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A7" s="12"/>
       <c r="B7" s="12"/>
       <c r="C7" s="12"/>
@@ -2061,7 +2102,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="8" spans="1:15" s="1" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:15" s="1" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8" s="12"/>
       <c r="B8" s="12"/>
       <c r="C8" s="12"/>
@@ -2090,7 +2131,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="9" spans="1:15" s="1" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:15" s="1" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A9" s="12"/>
       <c r="B9" s="12"/>
       <c r="C9" s="12"/>
@@ -2119,7 +2160,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="10" spans="1:15" s="1" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:15" s="1" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A10" s="12"/>
       <c r="B10" s="12"/>
       <c r="C10" s="12"/>
@@ -2148,20 +2189,20 @@
         <v>16</v>
       </c>
     </row>
-    <row r="11" spans="1:15" s="1" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:15" s="1" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A11" s="12"/>
       <c r="B11" s="12"/>
       <c r="C11" s="12"/>
       <c r="D11" s="12"/>
       <c r="E11" s="12"/>
       <c r="F11" s="12"/>
-      <c r="G11" s="14" t="s">
+      <c r="G11" s="11" t="s">
         <v>49</v>
       </c>
-      <c r="H11" s="11" t="s">
+      <c r="H11" s="14" t="s">
         <v>50</v>
       </c>
-      <c r="I11" s="11" t="s">
+      <c r="I11" s="14" t="s">
         <v>51</v>
       </c>
       <c r="J11" s="4" t="s">
@@ -2183,7 +2224,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="12" spans="1:15" s="1" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="12" spans="1:15" s="1" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A12" s="12"/>
       <c r="B12" s="12"/>
       <c r="C12" s="12"/>
@@ -2212,7 +2253,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="13" spans="1:15" s="1" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="13" spans="1:15" s="1" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A13" s="12"/>
       <c r="B13" s="12"/>
       <c r="C13" s="12"/>
@@ -2241,7 +2282,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="14" spans="1:15" s="1" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="14" spans="1:15" s="1" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A14" s="12"/>
       <c r="B14" s="12"/>
       <c r="C14" s="12"/>
@@ -2258,20 +2299,20 @@
       <c r="N14" s="5"/>
       <c r="O14" s="5"/>
     </row>
-    <row r="15" spans="1:15" s="1" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="15" spans="1:15" s="1" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A15" s="12"/>
       <c r="B15" s="12"/>
       <c r="C15" s="12"/>
-      <c r="D15" s="14"/>
-      <c r="E15" s="11"/>
-      <c r="F15" s="11"/>
-      <c r="G15" s="14" t="s">
+      <c r="D15" s="11"/>
+      <c r="E15" s="14"/>
+      <c r="F15" s="14"/>
+      <c r="G15" s="11" t="s">
         <v>61</v>
       </c>
-      <c r="H15" s="11" t="s">
+      <c r="H15" s="14" t="s">
         <v>62</v>
       </c>
-      <c r="I15" s="11" t="s">
+      <c r="I15" s="14" t="s">
         <v>63</v>
       </c>
       <c r="J15" s="4" t="s">
@@ -2293,7 +2334,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="16" spans="1:15" s="1" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="16" spans="1:15" s="1" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A16" s="12"/>
       <c r="B16" s="12"/>
       <c r="C16" s="12"/>
@@ -2322,7 +2363,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="17" spans="1:15" s="1" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="17" spans="1:15" s="1" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A17" s="12"/>
       <c r="B17" s="12"/>
       <c r="C17" s="12"/>
@@ -2351,7 +2392,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="18" spans="1:15" s="1" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="18" spans="1:15" s="1" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A18" s="12"/>
       <c r="B18" s="12"/>
       <c r="C18" s="12"/>
@@ -2380,7 +2421,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="19" spans="1:15" s="1" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="19" spans="1:15" s="1" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A19" s="12"/>
       <c r="B19" s="12"/>
       <c r="C19" s="12"/>
@@ -2409,7 +2450,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="20" spans="1:15" s="1" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="20" spans="1:15" s="1" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A20" s="12"/>
       <c r="B20" s="12"/>
       <c r="C20" s="12"/>
@@ -2438,7 +2479,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="21" spans="1:15" s="1" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="21" spans="1:15" s="1" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A21" s="12"/>
       <c r="B21" s="12"/>
       <c r="C21" s="12"/>
@@ -2467,16 +2508,16 @@
         <v>16</v>
       </c>
     </row>
-    <row r="22" spans="1:15" s="1" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="22" spans="1:15" s="1" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A22" s="12"/>
       <c r="B22" s="12"/>
       <c r="C22" s="12"/>
       <c r="D22" s="12"/>
       <c r="E22" s="12"/>
       <c r="F22" s="12"/>
-      <c r="G22" s="14"/>
-      <c r="H22" s="11"/>
-      <c r="I22" s="11"/>
+      <c r="G22" s="11"/>
+      <c r="H22" s="14"/>
+      <c r="I22" s="14"/>
       <c r="J22" s="4" t="s">
         <v>70</v>
       </c>
@@ -2496,7 +2537,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="23" spans="1:15" s="1" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="23" spans="1:15" s="1" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A23" s="13"/>
       <c r="B23" s="13"/>
       <c r="C23" s="13"/>
@@ -2525,24 +2566,24 @@
         <v>16</v>
       </c>
     </row>
-    <row r="24" spans="1:15" s="1" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A24" s="14" t="s">
+    <row r="24" spans="1:15" s="1" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A24" s="11" t="s">
         <v>73</v>
       </c>
-      <c r="B24" s="11"/>
-      <c r="C24" s="11"/>
-      <c r="D24" s="14" t="s">
+      <c r="B24" s="14"/>
+      <c r="C24" s="14"/>
+      <c r="D24" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="E24" s="11" t="s">
+      <c r="E24" s="14" t="s">
         <v>23</v>
       </c>
-      <c r="F24" s="11" t="s">
+      <c r="F24" s="14" t="s">
         <v>24</v>
       </c>
-      <c r="G24" s="14"/>
-      <c r="H24" s="11"/>
-      <c r="I24" s="11"/>
+      <c r="G24" s="11"/>
+      <c r="H24" s="14"/>
+      <c r="I24" s="14"/>
       <c r="J24" s="4"/>
       <c r="K24" s="5"/>
       <c r="L24" s="5"/>
@@ -2550,7 +2591,7 @@
       <c r="N24" s="5"/>
       <c r="O24" s="5"/>
     </row>
-    <row r="25" spans="1:15" s="1" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="25" spans="1:15" s="1" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A25" s="12"/>
       <c r="B25" s="12"/>
       <c r="C25" s="12"/>
@@ -2567,7 +2608,7 @@
       <c r="N25" s="5"/>
       <c r="O25" s="5"/>
     </row>
-    <row r="26" spans="1:15" s="1" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="26" spans="1:15" s="1" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A26" s="12"/>
       <c r="B26" s="12"/>
       <c r="C26" s="12"/>
@@ -2584,20 +2625,20 @@
       <c r="N26" s="5"/>
       <c r="O26" s="5"/>
     </row>
-    <row r="27" spans="1:15" s="1" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="27" spans="1:15" s="1" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A27" s="12"/>
       <c r="B27" s="12"/>
       <c r="C27" s="12"/>
       <c r="D27" s="12"/>
       <c r="E27" s="12"/>
       <c r="F27" s="12"/>
-      <c r="G27" s="14" t="s">
+      <c r="G27" s="11" t="s">
         <v>37</v>
       </c>
-      <c r="H27" s="11" t="s">
+      <c r="H27" s="14" t="s">
         <v>38</v>
       </c>
-      <c r="I27" s="11" t="s">
+      <c r="I27" s="14" t="s">
         <v>39</v>
       </c>
       <c r="J27" s="4" t="s">
@@ -2619,7 +2660,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="28" spans="1:15" s="1" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="28" spans="1:15" s="1" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A28" s="12"/>
       <c r="B28" s="12"/>
       <c r="C28" s="12"/>
@@ -2648,7 +2689,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="29" spans="1:15" s="1" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="29" spans="1:15" s="1" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A29" s="12"/>
       <c r="B29" s="12"/>
       <c r="C29" s="12"/>
@@ -2677,7 +2718,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="30" spans="1:15" s="1" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="30" spans="1:15" s="1" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A30" s="12"/>
       <c r="B30" s="12"/>
       <c r="C30" s="12"/>
@@ -2706,7 +2747,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="31" spans="1:15" s="1" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="31" spans="1:15" s="1" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A31" s="12"/>
       <c r="B31" s="12"/>
       <c r="C31" s="12"/>
@@ -2735,20 +2776,20 @@
         <v>16</v>
       </c>
     </row>
-    <row r="32" spans="1:15" s="1" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="32" spans="1:15" s="1" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A32" s="12"/>
       <c r="B32" s="12"/>
       <c r="C32" s="12"/>
       <c r="D32" s="12"/>
       <c r="E32" s="12"/>
       <c r="F32" s="12"/>
-      <c r="G32" s="14" t="s">
+      <c r="G32" s="11" t="s">
         <v>49</v>
       </c>
-      <c r="H32" s="11" t="s">
+      <c r="H32" s="14" t="s">
         <v>50</v>
       </c>
-      <c r="I32" s="11" t="s">
+      <c r="I32" s="14" t="s">
         <v>51</v>
       </c>
       <c r="J32" s="4" t="s">
@@ -2770,7 +2811,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="33" spans="1:15" s="1" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="33" spans="1:15" s="1" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A33" s="12"/>
       <c r="B33" s="12"/>
       <c r="C33" s="12"/>
@@ -2799,7 +2840,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="34" spans="1:15" s="1" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="34" spans="1:15" s="1" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A34" s="12"/>
       <c r="B34" s="12"/>
       <c r="C34" s="12"/>
@@ -2828,7 +2869,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="35" spans="1:15" s="1" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="35" spans="1:15" s="1" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A35" s="12"/>
       <c r="B35" s="12"/>
       <c r="C35" s="12"/>
@@ -2857,20 +2898,20 @@
         <v>16</v>
       </c>
     </row>
-    <row r="36" spans="1:15" s="1" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="36" spans="1:15" s="1" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A36" s="12"/>
       <c r="B36" s="12"/>
       <c r="C36" s="12"/>
-      <c r="D36" s="14"/>
-      <c r="E36" s="11"/>
-      <c r="F36" s="11"/>
-      <c r="G36" s="14" t="s">
+      <c r="D36" s="11"/>
+      <c r="E36" s="14"/>
+      <c r="F36" s="14"/>
+      <c r="G36" s="11" t="s">
         <v>61</v>
       </c>
-      <c r="H36" s="11" t="s">
+      <c r="H36" s="14" t="s">
         <v>62</v>
       </c>
-      <c r="I36" s="11" t="s">
+      <c r="I36" s="14" t="s">
         <v>63</v>
       </c>
       <c r="J36" s="4" t="s">
@@ -2892,7 +2933,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="37" spans="1:15" s="1" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="37" spans="1:15" s="1" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A37" s="12"/>
       <c r="B37" s="12"/>
       <c r="C37" s="12"/>
@@ -2921,7 +2962,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="38" spans="1:15" s="1" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="38" spans="1:15" s="1" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A38" s="12"/>
       <c r="B38" s="12"/>
       <c r="C38" s="12"/>
@@ -2950,7 +2991,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="39" spans="1:15" s="1" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="39" spans="1:15" s="1" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A39" s="12"/>
       <c r="B39" s="12"/>
       <c r="C39" s="12"/>
@@ -2979,7 +3020,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="40" spans="1:15" s="1" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="40" spans="1:15" s="1" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A40" s="12"/>
       <c r="B40" s="12"/>
       <c r="C40" s="12"/>
@@ -3008,7 +3049,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="41" spans="1:15" s="1" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="41" spans="1:15" s="1" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A41" s="12"/>
       <c r="B41" s="12"/>
       <c r="C41" s="12"/>
@@ -3037,7 +3078,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="42" spans="1:15" s="1" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="42" spans="1:15" s="1" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A42" s="12"/>
       <c r="B42" s="12"/>
       <c r="C42" s="12"/>
@@ -3066,16 +3107,16 @@
         <v>16</v>
       </c>
     </row>
-    <row r="43" spans="1:15" s="1" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="43" spans="1:15" s="1" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A43" s="12"/>
       <c r="B43" s="12"/>
       <c r="C43" s="12"/>
       <c r="D43" s="12"/>
       <c r="E43" s="12"/>
       <c r="F43" s="12"/>
-      <c r="G43" s="14"/>
-      <c r="H43" s="11"/>
-      <c r="I43" s="11"/>
+      <c r="G43" s="11"/>
+      <c r="H43" s="14"/>
+      <c r="I43" s="14"/>
       <c r="J43" s="4" t="s">
         <v>70</v>
       </c>
@@ -3095,7 +3136,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="44" spans="1:15" s="1" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="44" spans="1:15" s="1" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A44" s="13"/>
       <c r="B44" s="13"/>
       <c r="C44" s="13"/>
@@ -3124,7 +3165,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="45" spans="1:15" s="1" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="45" spans="1:15" s="1" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A45" s="4" t="s">
         <v>77</v>
       </c>
@@ -3155,7 +3196,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="46" spans="1:15" s="1" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="46" spans="1:15" s="1" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A46" s="4" t="s">
         <v>78</v>
       </c>
@@ -3174,7 +3215,7 @@
       <c r="N46" s="5"/>
       <c r="O46" s="5"/>
     </row>
-    <row r="47" spans="1:15" s="1" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="47" spans="1:15" s="1" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A47" s="4" t="s">
         <v>82</v>
       </c>
@@ -3193,7 +3234,7 @@
       <c r="N47" s="5"/>
       <c r="O47" s="5"/>
     </row>
-    <row r="48" spans="1:15" x14ac:dyDescent="0.45">
+    <row r="48" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A48" s="4" t="s">
         <v>80</v>
       </c>
@@ -3212,7 +3253,7 @@
       <c r="N48" s="5"/>
       <c r="O48" s="5"/>
     </row>
-    <row r="49" spans="1:15" x14ac:dyDescent="0.45">
+    <row r="49" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A49" s="7" t="s">
         <v>81</v>
       </c>
@@ -3233,7 +3274,7 @@
       <c r="N49" s="8"/>
       <c r="O49" s="8"/>
     </row>
-    <row r="50" spans="1:15" x14ac:dyDescent="0.45">
+    <row r="50" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A50" s="7" t="s">
         <v>85</v>
       </c>
@@ -3256,7 +3297,7 @@
       <c r="N50" s="8"/>
       <c r="O50" s="8"/>
     </row>
-    <row r="51" spans="1:15" x14ac:dyDescent="0.45">
+    <row r="51" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A51" s="7" t="s">
         <v>87</v>
       </c>
@@ -3279,7 +3320,7 @@
       <c r="N51" s="8"/>
       <c r="O51" s="8"/>
     </row>
-    <row r="52" spans="1:15" x14ac:dyDescent="0.45">
+    <row r="52" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A52" s="7" t="s">
         <v>91</v>
       </c>
@@ -3302,7 +3343,7 @@
       <c r="N52" s="8"/>
       <c r="O52" s="8"/>
     </row>
-    <row r="53" spans="1:15" x14ac:dyDescent="0.45">
+    <row r="53" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A53" s="7" t="s">
         <v>94</v>
       </c>
@@ -3323,8 +3364,73 @@
       <c r="N53" s="8"/>
       <c r="O53" s="8"/>
     </row>
+    <row r="54" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A54" s="7" t="s">
+        <v>97</v>
+      </c>
+      <c r="B54" s="8"/>
+      <c r="C54" s="8" t="s">
+        <v>90</v>
+      </c>
+      <c r="D54" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="E54" s="8"/>
+      <c r="F54" s="8" t="s">
+        <v>99</v>
+      </c>
+      <c r="G54" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="H54" s="8"/>
+      <c r="I54" s="8" t="s">
+        <v>92</v>
+      </c>
+      <c r="J54" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="K54" s="8"/>
+      <c r="L54" s="8" t="s">
+        <v>98</v>
+      </c>
+      <c r="M54" s="8"/>
+      <c r="N54" s="8"/>
+      <c r="O54" s="8"/>
+    </row>
   </sheetData>
   <mergeCells count="48">
+    <mergeCell ref="C24:C44"/>
+    <mergeCell ref="G43:G44"/>
+    <mergeCell ref="I15:I21"/>
+    <mergeCell ref="G15:G21"/>
+    <mergeCell ref="I11:I13"/>
+    <mergeCell ref="D3:D14"/>
+    <mergeCell ref="D15:D23"/>
+    <mergeCell ref="F15:F23"/>
+    <mergeCell ref="E36:E44"/>
+    <mergeCell ref="G6:G10"/>
+    <mergeCell ref="I6:I10"/>
+    <mergeCell ref="D36:D44"/>
+    <mergeCell ref="H43:H44"/>
+    <mergeCell ref="G24:G26"/>
+    <mergeCell ref="H32:H34"/>
+    <mergeCell ref="H36:H42"/>
+    <mergeCell ref="A24:A44"/>
+    <mergeCell ref="H22:H23"/>
+    <mergeCell ref="I24:I26"/>
+    <mergeCell ref="F36:F44"/>
+    <mergeCell ref="D24:D35"/>
+    <mergeCell ref="G27:G31"/>
+    <mergeCell ref="G32:G34"/>
+    <mergeCell ref="I32:I34"/>
+    <mergeCell ref="I22:I23"/>
+    <mergeCell ref="H24:H26"/>
+    <mergeCell ref="G36:G42"/>
+    <mergeCell ref="B3:B23"/>
+    <mergeCell ref="I36:I42"/>
+    <mergeCell ref="I3:I5"/>
+    <mergeCell ref="E24:E35"/>
+    <mergeCell ref="H11:H13"/>
     <mergeCell ref="A3:A23"/>
     <mergeCell ref="G11:G13"/>
     <mergeCell ref="E15:E23"/>
@@ -3341,38 +3447,6 @@
     <mergeCell ref="G3:G5"/>
     <mergeCell ref="H6:H10"/>
     <mergeCell ref="H15:H21"/>
-    <mergeCell ref="A24:A44"/>
-    <mergeCell ref="H22:H23"/>
-    <mergeCell ref="I24:I26"/>
-    <mergeCell ref="F36:F44"/>
-    <mergeCell ref="D24:D35"/>
-    <mergeCell ref="G27:G31"/>
-    <mergeCell ref="G32:G34"/>
-    <mergeCell ref="I32:I34"/>
-    <mergeCell ref="I22:I23"/>
-    <mergeCell ref="H24:H26"/>
-    <mergeCell ref="G36:G42"/>
-    <mergeCell ref="B3:B23"/>
-    <mergeCell ref="I36:I42"/>
-    <mergeCell ref="I3:I5"/>
-    <mergeCell ref="E24:E35"/>
-    <mergeCell ref="H11:H13"/>
-    <mergeCell ref="C24:C44"/>
-    <mergeCell ref="G43:G44"/>
-    <mergeCell ref="I15:I21"/>
-    <mergeCell ref="G15:G21"/>
-    <mergeCell ref="I11:I13"/>
-    <mergeCell ref="D3:D14"/>
-    <mergeCell ref="D15:D23"/>
-    <mergeCell ref="F15:F23"/>
-    <mergeCell ref="E36:E44"/>
-    <mergeCell ref="G6:G10"/>
-    <mergeCell ref="I6:I10"/>
-    <mergeCell ref="D36:D44"/>
-    <mergeCell ref="H43:H44"/>
-    <mergeCell ref="G24:G26"/>
-    <mergeCell ref="H32:H34"/>
-    <mergeCell ref="H36:H42"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <headerFooter>
